--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487415_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487415_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.7477</v>
+        <v>10.1441</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4448</v>
+        <v>5.5472</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3029</v>
+        <v>4.5969</v>
       </c>
       <c r="G2" t="n">
         <v>3.0975</v>
@@ -610,13 +610,13 @@
         <v>3.3294</v>
       </c>
       <c r="S2" t="n">
-        <v>0.83</v>
+        <v>1.2264</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4734</v>
+        <v>0.5758</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3566</v>
+        <v>0.6506</v>
       </c>
       <c r="V2" t="n">
         <v>2.4908</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.6853</v>
+        <v>8.111000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1665</v>
+        <v>5.8595</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5188</v>
+        <v>2.2515</v>
       </c>
       <c r="G3" t="n">
         <v>3.453</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1367</v>
+        <v>1.5624</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5121</v>
+        <v>1.2051</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6246</v>
+        <v>0.3573</v>
       </c>
       <c r="V3" t="n">
         <v>0.9412</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>J. CONNELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9786</v>
+        <v>5.3506</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6549</v>
+        <v>1.6534</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3236</v>
+        <v>3.6972</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2953</v>
+        <v>2.7077</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.649</v>
+        <v>2.8594</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3537</v>
+        <v>-0.1516</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.4494</v>
+        <v>1.5308</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.0604</v>
+        <v>2.2438</v>
       </c>
       <c r="L4" t="n">
-        <v>0.611</v>
+        <v>-0.713</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1541</v>
+        <v>1.1769</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4114</v>
+        <v>0.6156</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2573</v>
+        <v>0.5614</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5668</v>
+        <v>2.1543</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>2.546</v>
+        <v>3.1336</v>
       </c>
       <c r="S4" t="n">
-        <v>3.9746</v>
+        <v>0.8215</v>
       </c>
       <c r="T4" t="n">
-        <v>3.0836</v>
+        <v>0.2182</v>
       </c>
       <c r="U4" t="n">
-        <v>0.891</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7325</v>
+        <v>-0.3329</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7325</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CONNELL</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7751</v>
+        <v>2.8295</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4254</v>
+        <v>-1.4941</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3497</v>
+        <v>4.3236</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7077</v>
+        <v>-1.2953</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8594</v>
+        <v>-1.649</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1516</v>
+        <v>0.3537</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5308</v>
+        <v>-1.4494</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2438</v>
+        <v>-2.0604</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.713</v>
+        <v>0.611</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1769</v>
+        <v>0.1541</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6156</v>
+        <v>0.4114</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5614</v>
+        <v>-0.2573</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1543</v>
+        <v>1.5668</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1336</v>
+        <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7541</v>
+        <v>1.8256</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0098</v>
+        <v>0.9345</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2558</v>
+        <v>0.891</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3329</v>
+        <v>0.7325</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2166</v>
+        <v>0.7325</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7081</v>
+        <v>2.4713</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1679</v>
+        <v>1.6796</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5401</v>
+        <v>0.7917</v>
       </c>
       <c r="G6" t="n">
         <v>0.07729999999999999</v>
@@ -922,13 +922,13 @@
         <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>1.556</v>
+        <v>1.3192</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0882</v>
+        <v>0.5999</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4678</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8837</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7399</v>
+        <v>2.0616</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3734</v>
+        <v>1.1762</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1133</v>
+        <v>0.8855</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6052</v>
+        <v>-3.745</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6363</v>
+        <v>1.7374</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0311</v>
+        <v>-5.4824</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0532</v>
+        <v>-2.4815</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1551</v>
+        <v>1.5311</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.102</v>
+        <v>-4.0126</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.448</v>
+        <v>-1.2635</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4812</v>
+        <v>0.2062</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9292</v>
+        <v>-1.4698</v>
       </c>
       <c r="P7" t="n">
+        <v>1.9585</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9792</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-3.917</v>
       </c>
       <c r="R7" t="n">
         <v>2.9377</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0474</v>
+        <v>0.8066</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2151</v>
+        <v>0.3788</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8323</v>
+        <v>0.4279</v>
       </c>
       <c r="V7" t="n">
-        <v>0.06660000000000001</v>
+        <v>3.0415</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2754</v>
+        <v>4.2581</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2088</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7295</v>
+        <v>1.4772</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3049</v>
+        <v>-1.4757</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4245</v>
+        <v>2.9529</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5981</v>
+        <v>0.6052</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4924</v>
+        <v>1.6363</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1057</v>
+        <v>-1.0311</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2554</v>
+        <v>1.0532</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2862</v>
+        <v>1.1551</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0308</v>
+        <v>-0.102</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3427</v>
+        <v>-0.448</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2062</v>
+        <v>0.4812</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1364</v>
+        <v>-0.9292</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1751</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7834</v>
+        <v>2.9377</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2399</v>
+        <v>1.7847</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0081</v>
+        <v>1.1127</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2318</v>
+        <v>0.672</v>
       </c>
       <c r="V8" t="n">
         <v>0.06660000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.2088</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4919</v>
+        <v>1.2224</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7668</v>
+        <v>-0.3091</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7251</v>
+        <v>1.5314</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.745</v>
+        <v>1.5981</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7374</v>
+        <v>1.4924</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.4824</v>
+        <v>0.1057</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.4815</v>
+        <v>1.2554</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5311</v>
+        <v>1.2862</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.0126</v>
+        <v>-0.0308</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2635</v>
+        <v>0.3427</v>
       </c>
       <c r="N9" t="n">
         <v>0.2062</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4698</v>
+        <v>0.1364</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9585</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9377</v>
+        <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2369</v>
+        <v>0.7328</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0306</v>
+        <v>0.394</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2675</v>
+        <v>0.3388</v>
       </c>
       <c r="V9" t="n">
-        <v>3.0415</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>4.2581</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.295</v>
+        <v>1.0193</v>
       </c>
       <c r="E10" t="n">
-        <v>1.289</v>
+        <v>0.8797</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006</v>
+        <v>0.1397</v>
       </c>
       <c r="G10" t="n">
         <v>0.6802</v>
@@ -1234,13 +1234,13 @@
         <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7649</v>
+        <v>0.4892</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6516</v>
+        <v>0.2423</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1132</v>
+        <v>0.2469</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5417</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5493</v>
+        <v>-0.2644</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2211</v>
+        <v>0.4258</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7704</v>
+        <v>-0.6902</v>
       </c>
       <c r="G11" t="n">
         <v>0.7889</v>
@@ -1312,13 +1312,13 @@
         <v>0.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1424</v>
+        <v>0.1425</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0594</v>
+        <v>0.1453</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.083</v>
+        <v>-0.0028</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.557</v>
+        <v>-1.0011</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2038</v>
+        <v>-1.4875</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6468</v>
+        <v>0.4864</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1664</v>
@@ -1390,13 +1390,13 @@
         <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7006</v>
+        <v>1.2566</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0288</v>
+        <v>0.7452</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6718</v>
+        <v>0.5114</v>
       </c>
       <c r="V12" t="n">
         <v>-1.483</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.6661</v>
+        <v>-1.0429</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0367</v>
+        <v>0.4461</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7028</v>
+        <v>-1.489</v>
       </c>
       <c r="G13" t="n">
         <v>0.0004</v>
@@ -1468,13 +1468,13 @@
         <v>0.5875</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4867</v>
+        <v>0.1364</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3564</v>
+        <v>0.0529</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1303</v>
+        <v>0.0835</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7673</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.3787</v>
+        <v>32.37859999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>12.9008</v>
+        <v>12.9011</v>
       </c>
       <c r="F14" t="n">
         <v>19.4776</v>
@@ -1525,7 +1525,7 @@
         <v>14.9364</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.957399999999999</v>
+        <v>-4.957399999999998</v>
       </c>
       <c r="M14" t="n">
         <v>-3.177500000000001</v>
@@ -1546,19 +1546,19 @@
         <v>23.5016</v>
       </c>
       <c r="S14" t="n">
-        <v>12.1038</v>
+        <v>12.1039</v>
       </c>
       <c r="T14" t="n">
-        <v>6.604700000000001</v>
+        <v>6.6047</v>
       </c>
       <c r="U14" t="n">
-        <v>5.4991</v>
+        <v>5.499200000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.722300000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>8.068299999999999</v>
+        <v>8.068300000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-6.345700000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2657</v>
+        <v>0.074</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6204</v>
+        <v>-0.518</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8861</v>
+        <v>0.5921</v>
       </c>
       <c r="G15" t="n">
         <v>1.1066</v>
@@ -1624,13 +1624,13 @@
         <v>0.5875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6695</v>
+        <v>-0.8612</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.594</v>
+        <v>-0.4917</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0755</v>
+        <v>-0.3695</v>
       </c>
       <c r="V15" t="n">
         <v>0.2203</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X. IGOA ENDJILO</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7603</v>
+        <v>-0.7472</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5438</v>
+        <v>-0.3505</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7835</v>
+        <v>-0.3967</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0038</v>
+        <v>1.6407</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6812</v>
+        <v>-1.6226</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6774</v>
+        <v>3.2632</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2225</v>
+        <v>2.4303</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3437</v>
+        <v>0.1429</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1212</v>
+        <v>2.2873</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2187</v>
+        <v>-0.7896</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3375</v>
+        <v>-1.7655</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5562</v>
+        <v>0.9759</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5875</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>-1.5668</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7773</v>
+        <v>-1.6747</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0288</v>
+        <v>-0.881</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8061</v>
+        <v>-0.7937</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6083</v>
+        <v>-0.3214</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6083</v>
+        <v>-0.3329</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>X. IGOA ENDJILO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1077</v>
+        <v>-1.1208</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6575</v>
+        <v>-1.8509</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4501</v>
+        <v>0.7301</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6407</v>
+        <v>-0.0038</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6226</v>
+        <v>-0.6812</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2632</v>
+        <v>0.6774</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4303</v>
+        <v>-0.2225</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1429</v>
+        <v>-0.3437</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2873</v>
+        <v>0.1212</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7896</v>
+        <v>0.2187</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7655</v>
+        <v>-0.3375</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9759</v>
+        <v>0.5562</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.5668</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0352</v>
+        <v>-1.1377</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.188</v>
+        <v>-0.2782</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8471</v>
+        <v>-0.8596</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3214</v>
+        <v>0.6083</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3329</v>
+        <v>0.6083</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. IGLESIAS VALDERRAMA</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1078</v>
+        <v>-2.8481</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3369</v>
+        <v>-2.1058</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7708</v>
+        <v>-0.7423</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0524</v>
+        <v>-2.9811</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.014</v>
+        <v>-1.8342</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0664</v>
+        <v>-1.1468</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6358</v>
+        <v>-1.5061</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5954</v>
+        <v>0.3385</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0404</v>
+        <v>-1.8446</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5834</v>
+        <v>-1.4749</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6093</v>
+        <v>-2.1728</v>
       </c>
       <c r="O18" t="n">
-        <v>0.026</v>
+        <v>0.6978</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1958</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9792</v>
+        <v>-2.546</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7834</v>
+        <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0268</v>
+        <v>-1.4464</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3276</v>
+        <v>-0.7622</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6992</v>
+        <v>-0.6841</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.9376</v>
+        <v>2.1669</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6659</v>
+        <v>2.7086</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2717</v>
+        <v>-0.5417</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>M. IGLESIAS VALDERRAMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2888</v>
+        <v>-3.2055</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4128</v>
+        <v>-1.5416</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.876</v>
+        <v>-1.6639</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9811</v>
+        <v>0.0524</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8342</v>
+        <v>-0.014</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1468</v>
+        <v>0.0664</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5061</v>
+        <v>0.6358</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3385</v>
+        <v>0.5954</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8446</v>
+        <v>0.0404</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4749</v>
+        <v>-0.5834</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.1728</v>
+        <v>-0.6093</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6978</v>
+        <v>0.026</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5875</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.546</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9585</v>
+        <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.887</v>
+        <v>-1.1245</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0692</v>
+        <v>-0.5323</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8178</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1669</v>
+        <v>-1.9376</v>
       </c>
       <c r="W19" t="n">
-        <v>2.7086</v>
+        <v>-0.6659</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5417</v>
+        <v>-1.2717</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.913</v>
+        <v>-4.0062</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6892</v>
+        <v>-1.9962</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2238</v>
+        <v>-2.0099</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9554</v>
@@ -2014,13 +2014,13 @@
         <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1192</v>
+        <v>-0.2123</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1476</v>
+        <v>-0.1594</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2668</v>
+        <v>-0.0529</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2717</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>R. ESPINOZA OROZCO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0996</v>
+        <v>-4.041</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.413</v>
+        <v>-1.898</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3134</v>
+        <v>-2.143</v>
       </c>
       <c r="G21" t="n">
-        <v>0.526</v>
+        <v>-1.1019</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1725</v>
+        <v>-3.4716</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6985</v>
+        <v>2.3697</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8489</v>
+        <v>0.9188</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1362</v>
+        <v>-1.026</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9852</v>
+        <v>1.9447</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3229</v>
+        <v>-2.0207</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0363</v>
+        <v>-2.4456</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7134</v>
+        <v>0.4249</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.546</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5045</v>
+        <v>-3.5253</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9585</v>
+        <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6927</v>
+        <v>-1.6555</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4256</v>
+        <v>-0.5082</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7329</v>
+        <v>-1.1473</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3868</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.3318</v>
+        <v>1.2166</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0551</v>
+        <v>-0.5417</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. ESPINOZA OROZCO</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5397</v>
+        <v>-4.4876</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1027</v>
+        <v>-5.106</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.437</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1019</v>
+        <v>0.526</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.4716</v>
+        <v>-2.1725</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3697</v>
+        <v>2.6985</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9188</v>
+        <v>1.8489</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.026</v>
+        <v>-0.1362</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9447</v>
+        <v>1.9852</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0207</v>
+        <v>-1.3229</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.4456</v>
+        <v>-2.0363</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4249</v>
+        <v>0.7134</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9585</v>
+        <v>-2.546</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.5253</v>
+        <v>-4.5045</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5668</v>
+        <v>1.9585</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1542</v>
+        <v>-1.0807</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7128</v>
+        <v>-1.1186</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4413</v>
+        <v>0.0379</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6749000000000001</v>
+        <v>-1.3868</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2166</v>
+        <v>-1.3318</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5417</v>
+        <v>-0.0551</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7021</v>
+        <v>-4.9907</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1438</v>
+        <v>-1.8601</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5583</v>
+        <v>-3.1306</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6189</v>
@@ -2248,13 +2248,13 @@
         <v>1.5668</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3123</v>
+        <v>-1.6009</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1764</v>
+        <v>-0.5399</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4887</v>
+        <v>-1.061</v>
       </c>
       <c r="V23" t="n">
         <v>2.1669</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.1254</v>
+        <v>-7.0055</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1657</v>
+        <v>-2.8587</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9597</v>
+        <v>-4.1469</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4661</v>
@@ -2326,13 +2326,13 @@
         <v>0.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4298</v>
+        <v>-1.3099</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5346</v>
+        <v>-0.2276</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8952</v>
+        <v>-1.0823</v>
       </c>
       <c r="V24" t="n">
         <v>-2.642</v>
@@ -2359,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-32.3787</v>
+        <v>-32.3786</v>
       </c>
       <c r="E25" t="n">
         <v>-20.0858</v>
@@ -2404,13 +2404,13 @@
         <v>11.7509</v>
       </c>
       <c r="S25" t="n">
-        <v>-12.104</v>
+        <v>-12.1038</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.499</v>
+        <v>-5.4991</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.6048</v>
+        <v>-6.6047</v>
       </c>
       <c r="V25" t="n">
         <v>-1.7222</v>
